--- a/projetos/renova-cell/06-campanhas/meta-ads/onda-0-montagem.xlsx
+++ b/projetos/renova-cell/06-campanhas/meta-ads/onda-0-montagem.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>https://SEU_DOMINIO/quiz</t>
+          <t>https://renova-cell.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>https://SEU_DOMINIO/quiz</t>
+          <t>https://renova-cell.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>https://SEU_DOMINIO/quiz</t>
+          <t>https://renova-cell.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>https://SEU_DOMINIO/quiz</t>
+          <t>https://renova-cell.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>https://SEU_DOMINIO/quiz</t>
+          <t>https://renova-cell.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>https://SEU_DOMINIO/quiz</t>
+          <t>https://renova-cell.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>https://SEU_DOMINIO/quiz</t>
+          <t>https://renova-cell.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>https://SEU_DOMINIO/quiz</t>
+          <t>https://renova-cell.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>https://SEU_DOMINIO/quiz</t>
+          <t>https://renova-cell.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>https://SEU_DOMINIO/quiz</t>
+          <t>https://renova-cell.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>https://SEU_DOMINIO/quiz</t>
+          <t>https://renova-cell.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>https://SEU_DOMINIO/quiz</t>
+          <t>https://renova-cell.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>https://SEU_DOMINIO/quiz</t>
+          <t>https://renova-cell.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>https://SEU_DOMINIO/quiz</t>
+          <t>https://renova-cell.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>https://SEU_DOMINIO/quiz</t>
+          <t>https://renova-cell.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>https://SEU_DOMINIO/quiz</t>
+          <t>https://renova-cell.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>https://SEU_DOMINIO/quiz</t>
+          <t>https://renova-cell.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>https://SEU_DOMINIO/quiz</t>
+          <t>https://renova-cell.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>https://SEU_DOMINIO/offer</t>
+          <t>https://renova-cell.vercel.app/offer</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>https://SEU_DOMINIO/offer</t>
+          <t>https://renova-cell.vercel.app/offer</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>https://SEU_DOMINIO/offer</t>
+          <t>https://renova-cell.vercel.app/offer</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>https://SEU_DOMINIO/offer</t>
+          <t>https://renova-cell.vercel.app/offer</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">

--- a/projetos/renova-cell/06-campanhas/meta-ads/onda-0-montagem.xlsx
+++ b/projetos/renova-cell/06-campanhas/meta-ads/onda-0-montagem.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>https://renova-cell.vercel.app/quiz</t>
+          <t>https://vitalrise.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>https://renova-cell.vercel.app/quiz</t>
+          <t>https://vitalrise.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>https://renova-cell.vercel.app/quiz</t>
+          <t>https://vitalrise.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Some things are nobody else's business. RENOVA CELL ships in a plain box with no product name on the outside.
+          <t>Some things are nobody else's business. VitalRise ships in a plain box with no product name on the outside.
 Free shipping, delivered in up to 2 business days with tracking. Buy once, or subscribe and it arrives again when you run out. Cancel anytime.
 Take the 60-second quiz to find your plan. 30-day money-back guarantee.
 Individual results vary. These statements have not been evaluated by the Food and Drug Administration. This product is not intended to diagnose, treat, cure, or prevent any disease.</t>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>https://renova-cell.vercel.app/quiz</t>
+          <t>https://vitalrise.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Some things are nobody else's business. RENOVA CELL ships in a plain box with no product name on the outside.
+          <t>Some things are nobody else's business. VitalRise ships in a plain box with no product name on the outside.
 Free shipping, delivered in up to 2 business days with tracking. Buy once, or subscribe and it arrives again when you run out. Cancel anytime.
 Take the 60-second quiz to find your plan. 30-day money-back guarantee.
 Individual results vary. These statements have not been evaluated by the Food and Drug Administration. This product is not intended to diagnose, treat, cure, or prevent any disease.</t>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>https://renova-cell.vercel.app/quiz</t>
+          <t>https://vitalrise.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Some things are nobody else's business. RENOVA CELL ships in a plain box with no product name on the outside.
+          <t>Some things are nobody else's business. VitalRise ships in a plain box with no product name on the outside.
 Free shipping, delivered in up to 2 business days with tracking. Buy once, or subscribe and it arrives again when you run out. Cancel anytime.
 Take the 60-second quiz to find your plan. 30-day money-back guarantee.
 Individual results vary. These statements have not been evaluated by the Food and Drug Administration. This product is not intended to diagnose, treat, cure, or prevent any disease.</t>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>https://renova-cell.vercel.app/quiz</t>
+          <t>https://vitalrise.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>https://renova-cell.vercel.app/quiz</t>
+          <t>https://vitalrise.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>https://renova-cell.vercel.app/quiz</t>
+          <t>https://vitalrise.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>https://renova-cell.vercel.app/quiz</t>
+          <t>https://vitalrise.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>https://renova-cell.vercel.app/quiz</t>
+          <t>https://vitalrise.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>https://renova-cell.vercel.app/quiz</t>
+          <t>https://vitalrise.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>https://renova-cell.vercel.app/quiz</t>
+          <t>https://vitalrise.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>[Legenda do próprio criador, aprovada pela marca — só experiência real, sem resultado.] Example: "I've been adding RENOVA CELL to my morning coffee for 4 weeks. One scoop and done. Free shipping, and it came in a plain box. #ad"
+          <t>[Legenda do próprio criador, aprovada pela marca — só experiência real, sem resultado.] Example: "I've been adding VitalRise to my morning coffee for 4 weeks. One scoop and done. Free shipping, and it came in a plain box. #ad"
 Individual results vary. These statements have not been evaluated by the Food and Drug Administration. This product is not intended to diagnose, treat, cure, or prevent any disease.</t>
         </is>
       </c>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>https://renova-cell.vercel.app/quiz</t>
+          <t>https://vitalrise.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>[Legenda do próprio criador, aprovada pela marca — só experiência real, sem resultado.] Example: "I've been adding RENOVA CELL to my morning coffee for 4 weeks. One scoop and done. Free shipping, and it came in a plain box. #ad"
+          <t>[Legenda do próprio criador, aprovada pela marca — só experiência real, sem resultado.] Example: "I've been adding VitalRise to my morning coffee for 4 weeks. One scoop and done. Free shipping, and it came in a plain box. #ad"
 Individual results vary. These statements have not been evaluated by the Food and Drug Administration. This product is not intended to diagnose, treat, cure, or prevent any disease.</t>
         </is>
       </c>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>https://renova-cell.vercel.app/quiz</t>
+          <t>https://vitalrise.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>[Legenda do próprio criador, aprovada pela marca — só experiência real, sem resultado.] Example: "I've been adding RENOVA CELL to my morning coffee for 4 weeks. One scoop and done. Free shipping, and it came in a plain box. #ad"
+          <t>[Legenda do próprio criador, aprovada pela marca — só experiência real, sem resultado.] Example: "I've been adding VitalRise to my morning coffee for 4 weeks. One scoop and done. Free shipping, and it came in a plain box. #ad"
 Individual results vary. These statements have not been evaluated by the Food and Drug Administration. This product is not intended to diagnose, treat, cure, or prevent any disease.</t>
         </is>
       </c>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>https://renova-cell.vercel.app/quiz</t>
+          <t>https://vitalrise.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>https://renova-cell.vercel.app/quiz</t>
+          <t>https://vitalrise.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>https://renova-cell.vercel.app/quiz</t>
+          <t>https://vitalrise.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>https://renova-cell.vercel.app/quiz</t>
+          <t>https://vitalrise.vercel.app/quiz</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Still thinking about it? Try RENOVA CELL for 30 days. If it's not for you, email us and we'll refund your first order.
+          <t>Still thinking about it? Try VitalRise for 30 days. If it's not for you, email us and we'll refund your first order.
 Free shipping, delivered in up to 2 business days in discreet packaging.
 Individual results vary. These statements have not been evaluated by the Food and Drug Administration. This product is not intended to diagnose, treat, cure, or prevent any disease.</t>
         </is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>https://renova-cell.vercel.app/offer</t>
+          <t>https://vitalrise.vercel.app/offer</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>https://renova-cell.vercel.app/offer</t>
+          <t>https://vitalrise.vercel.app/offer</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>https://renova-cell.vercel.app/offer</t>
+          <t>https://vitalrise.vercel.app/offer</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Cupom RENOVA10 (quem iniciou o checkout)</t>
+          <t>Cupom VITAL10 (quem iniciou o checkout)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2578,19 +2578,19 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Arte: "10% off your first payment · code RENOVA10" + produto</t>
+          <t>Arte: "10% off your first payment · code VITAL10" + produto</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Your plan is still waiting. Use code RENOVA10 for 10% off your first payment.
+          <t>Your plan is still waiting. Use code VITAL10 for 10% off your first payment.
 Free shipping in up to 2 business days, discreet packaging, 30-day money-back guarantee.
 Individual results vary. These statements have not been evaluated by the Food and Drug Administration. This product is not intended to diagnose, treat, cure, or prevent any disease.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10% off with RENOVA10</t>
+          <t>10% off with VITAL10</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>https://renova-cell.vercel.app/offer</t>
+          <t>https://vitalrise.vercel.app/offer</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Chaves Stripe live + npm run stripe:setup (preços e cupom RENOVA10)</t>
+          <t>Chaves Stripe live + npm run stripe:setup (preços e cupom VITAL10)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
